--- a/fuction_ensemble/redes-ensemble-s/Teste05/content/results/metrics_7_6.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste05/content/results/metrics_7_6.xlsx
@@ -513,936 +513,936 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_7_6_24</t>
+          <t>model_7_6_12</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9999999979463728</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6649857041765251</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9999999938545842</v>
+        <v>0.9999946262773536</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999999989755225</v>
+        <v>0.9999999026688069</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999999962726565</v>
+        <v>0.9999993129615257</v>
       </c>
       <c r="G2" t="n">
-        <v>1.219121804040142e-09</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1988789578648563</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I2" t="n">
-        <v>5.799892496302841e-09</v>
+        <v>6.50011503440052e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>7.832359004230986e-10</v>
+        <v>9.281554796456152e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>3.29156419836297e-09</v>
+        <v>3.713185230149885e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>9.412676949373663e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.491592479142063e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000000001202123</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O2" t="n">
-        <v>3.640236799571982e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P2" t="n">
-        <v>171.0502701403184</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q2" t="n">
-        <v>250.2771987567515</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_7_6_23</t>
+          <t>model_7_6_22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9999999978827315</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6649844006168342</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9999999941415472</v>
+        <v>0.9999946262773536</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999999986292102</v>
+        <v>0.9999999026688069</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999999962764765</v>
+        <v>0.9999993129615257</v>
       </c>
       <c r="G3" t="n">
-        <v>1.256902011929078e-09</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1988797317141996</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I3" t="n">
-        <v>5.529063808069407e-09</v>
+        <v>6.50011503440052e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.04799934370773e-09</v>
+        <v>9.281554796456152e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.288190738665272e-09</v>
+        <v>3.713185230149885e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>9.595771871341673e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.545281387885985e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000000001239377</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O3" t="n">
-        <v>3.696211356312495e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P3" t="n">
-        <v>170.9892317285834</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q3" t="n">
-        <v>250.2161603450164</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_7_6_22</t>
+          <t>model_7_6_21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9999999977618063</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6649832799166758</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9999999943988469</v>
+        <v>0.9999946262773536</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9999999981253139</v>
+        <v>0.9999999026688069</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9999999961954604</v>
+        <v>0.9999993129615257</v>
       </c>
       <c r="G4" t="n">
-        <v>1.328688499197209e-09</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1988803970102254</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I4" t="n">
-        <v>5.28623063478596e-09</v>
+        <v>6.50011503440052e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.433239219867182e-09</v>
+        <v>9.281554796456152e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>3.359734927326571e-09</v>
+        <v>3.713185230149885e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>9.785026764426299e-06</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.645117966811512e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000000001310162</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O4" t="n">
-        <v>3.80029818509309e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P4" t="n">
-        <v>170.8781469440987</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q4" t="n">
-        <v>250.1050755605317</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_7_6_21</t>
+          <t>model_7_6_20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9999999975995891</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6649817533283686</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9999999947292836</v>
+        <v>0.9999946262773536</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9999999974312288</v>
+        <v>0.9999999026688069</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9999999960735737</v>
+        <v>0.9999993129615257</v>
       </c>
       <c r="G5" t="n">
-        <v>1.424987605983738e-09</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1988813032589897</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I5" t="n">
-        <v>4.974372702346925e-09</v>
+        <v>6.50011503440052e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.963882794650341e-09</v>
+        <v>9.281554796456152e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.467371349995052e-09</v>
+        <v>3.713185230149885e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.003039767243353e-05</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>3.774900801324106e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000000001405118</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O5" t="n">
-        <v>3.93560614355839e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P5" t="n">
-        <v>170.7382054416378</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q5" t="n">
-        <v>249.9651340580708</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_7_6_20</t>
+          <t>model_7_6_19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9999999973618292</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6649801354551137</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D6" t="n">
-        <v>0.999999995029643</v>
+        <v>0.9999946262773536</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9999999965095724</v>
+        <v>0.9999999026688069</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9999999958340886</v>
+        <v>0.9999993129615257</v>
       </c>
       <c r="G6" t="n">
-        <v>1.56613211295838e-09</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1988822636984424</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I6" t="n">
-        <v>4.690900809980307e-09</v>
+        <v>6.50011503440052e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.66850967549086e-09</v>
+        <v>9.281554796456152e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.678857241550062e-09</v>
+        <v>3.713185230149885e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.034889045803082e-05</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>3.957438708253584e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000000001544295</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O6" t="n">
-        <v>4.125915067091415e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P6" t="n">
-        <v>170.5493137592333</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q6" t="n">
-        <v>249.7762423756664</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_7_6_19</t>
+          <t>model_7_6_18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9999999970544222</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6649782324289829</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9999999954171539</v>
+        <v>0.9999946262773536</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9999999952572528</v>
+        <v>0.9999999026688069</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9999999954981083</v>
+        <v>0.9999993129615257</v>
       </c>
       <c r="G7" t="n">
-        <v>1.748622208710895e-09</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>0.19888339341696</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I7" t="n">
-        <v>4.325177603624797e-09</v>
+        <v>6.50011503440052e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>3.625935876299049e-09</v>
+        <v>9.281554796456152e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>3.975556739961923e-09</v>
+        <v>3.713185230149885e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.060772980916579e-05</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>4.181653032845856e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000000001724241</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O7" t="n">
-        <v>4.359674659669217e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P7" t="n">
-        <v>170.3288753368196</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q7" t="n">
-        <v>249.5558039532526</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_7_6_18</t>
+          <t>model_7_6_17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.999999996621426</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6649758850698158</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9999999958382729</v>
+        <v>0.9999946262773536</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9999999935857667</v>
+        <v>0.9999999026688069</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9999999950005226</v>
+        <v>0.9999993129615257</v>
       </c>
       <c r="G8" t="n">
-        <v>2.005667431918536e-09</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1988847869107623</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I8" t="n">
-        <v>3.927735806609346e-09</v>
+        <v>6.50011503440052e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>4.903824172578374e-09</v>
+        <v>9.281554796456152e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.414967515545126e-09</v>
+        <v>3.713185230149885e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>1.101342113503319e-05</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>4.478467853985931e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000000001977702</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O8" t="n">
-        <v>4.669125502236608e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P8" t="n">
-        <v>170.054577895663</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q8" t="n">
-        <v>249.281506512096</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_7_6_17</t>
+          <t>model_7_6_16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9999999960441921</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6649734966992724</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9999999962171245</v>
+        <v>0.9999946262773536</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9999999914322077</v>
+        <v>0.9999999026688069</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9999999942707118</v>
+        <v>0.9999993129615257</v>
       </c>
       <c r="G9" t="n">
-        <v>2.348338478881625e-09</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>0.198886204750689</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I9" t="n">
-        <v>3.57018496489948e-09</v>
+        <v>6.50011503440052e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>6.550267994793579e-09</v>
+        <v>9.281554796456152e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.059453085648263e-09</v>
+        <v>3.713185230149885e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>1.142805626876113e-05</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.845965826212175e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000000002315595</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O9" t="n">
-        <v>5.052268623966199e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P9" t="n">
-        <v>169.7391155782345</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q9" t="n">
-        <v>248.9660441946675</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_7_6_16</t>
+          <t>model_7_6_15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9999999952903703</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6649709603547433</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9999999965785304</v>
+        <v>0.9999946262773536</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9999999887117977</v>
+        <v>0.9999999026688069</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9999999932853746</v>
+        <v>0.9999993129615257</v>
       </c>
       <c r="G10" t="n">
-        <v>2.795839627714985e-09</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1988877104343658</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I10" t="n">
-        <v>3.229098861931921e-09</v>
+        <v>6.50011503440052e-07</v>
       </c>
       <c r="J10" t="n">
-        <v>8.630081971929277e-09</v>
+        <v>9.281554796456152e-08</v>
       </c>
       <c r="K10" t="n">
-        <v>5.9295904169306e-09</v>
+        <v>3.713185230149885e-07</v>
       </c>
       <c r="L10" t="n">
-        <v>1.184583418862427e-05</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>5.287569978463628e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000000002756856</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O10" t="n">
-        <v>5.512672779225614e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P10" t="n">
-        <v>169.3902667439512</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q10" t="n">
-        <v>248.6171953603842</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_7_6_15</t>
+          <t>model_7_6_14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9999999942874115</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6649679974544365</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9999999969418167</v>
+        <v>0.9999946262773536</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9999999851401928</v>
+        <v>0.9999999026688069</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9999999919334613</v>
+        <v>0.9999993129615257</v>
       </c>
       <c r="G11" t="n">
-        <v>3.391239290046957e-09</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1988894693399786</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I11" t="n">
-        <v>2.886238268493478e-09</v>
+        <v>6.50011503440052e-07</v>
       </c>
       <c r="J11" t="n">
-        <v>1.136065345997875e-08</v>
+        <v>9.281554796456152e-08</v>
       </c>
       <c r="K11" t="n">
-        <v>7.123445864236114e-09</v>
+        <v>3.713185230149885e-07</v>
       </c>
       <c r="L11" t="n">
-        <v>1.236676754142635e-05</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>5.823434802628906e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000000003343954</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O11" t="n">
-        <v>6.071350478348716e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P11" t="n">
-        <v>169.0041408201482</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q11" t="n">
-        <v>248.2310694365812</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_7_6_14</t>
+          <t>model_7_6_13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.999999993013617</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6649643810266468</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D12" t="n">
-        <v>0.99999999732278</v>
+        <v>0.9999946262773536</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9999999805669848</v>
+        <v>0.9999999026688069</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9999999901574302</v>
+        <v>0.9999993129615257</v>
       </c>
       <c r="G12" t="n">
-        <v>4.147418759979655e-09</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1988916162077362</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I12" t="n">
-        <v>2.526694507735765e-09</v>
+        <v>6.50011503440052e-07</v>
       </c>
       <c r="J12" t="n">
-        <v>1.485697282548813e-08</v>
+        <v>9.281554796456152e-08</v>
       </c>
       <c r="K12" t="n">
-        <v>8.691833666611947e-09</v>
+        <v>3.713185230149885e-07</v>
       </c>
       <c r="L12" t="n">
-        <v>1.29445705686221e-05</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M12" t="n">
-        <v>6.440045620940628e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N12" t="n">
-        <v>1.00000000408959</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O12" t="n">
-        <v>6.714211695756325e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P12" t="n">
-        <v>168.6015593635283</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q12" t="n">
-        <v>247.8284879799613</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_7_6_13</t>
+          <t>model_7_6_23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9999999913793833</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6649603635320136</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D13" t="n">
-        <v>0.999999997709339</v>
+        <v>0.9999946262773536</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9999999748187606</v>
+        <v>0.9999999026688069</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9999999878757564</v>
+        <v>0.9999993129615257</v>
       </c>
       <c r="G13" t="n">
-        <v>5.11757045478845e-09</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1988940011660972</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I13" t="n">
-        <v>2.161869555436673e-09</v>
+        <v>6.50011503440052e-07</v>
       </c>
       <c r="J13" t="n">
-        <v>1.925161825749742e-08</v>
+        <v>9.281554796456152e-08</v>
       </c>
       <c r="K13" t="n">
-        <v>1.070674753361068e-08</v>
+        <v>3.713185230149885e-07</v>
       </c>
       <c r="L13" t="n">
-        <v>1.395810571392945e-05</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>7.153719630226257e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000000005046215</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O13" t="n">
-        <v>7.458268285126108e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P13" t="n">
-        <v>168.1811720621293</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q13" t="n">
-        <v>247.4081006785623</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>model_7_6_12</t>
+          <t>model_7_6_24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9999999892936626</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6649559033689824</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9999999980287824</v>
+        <v>0.9999946262773536</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9999999674768401</v>
+        <v>0.9999999026688069</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9999999848683636</v>
+        <v>0.9999993129615257</v>
       </c>
       <c r="G14" t="n">
-        <v>6.355744358795447e-09</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1988966489115415</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I14" t="n">
-        <v>1.860386813590581e-09</v>
+        <v>6.50011503440052e-07</v>
       </c>
       <c r="J14" t="n">
-        <v>2.486467997776848e-08</v>
+        <v>9.281554796456152e-08</v>
       </c>
       <c r="K14" t="n">
-        <v>1.336253339567953e-08</v>
+        <v>3.713185230149885e-07</v>
       </c>
       <c r="L14" t="n">
-        <v>1.538791782170727e-05</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>7.97229224175547e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000000006267124</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O14" t="n">
-        <v>8.311689227407024e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P14" t="n">
-        <v>167.7478136190693</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q14" t="n">
-        <v>246.9747422355023</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_7_6_11</t>
+          <t>model_7_6_10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9999999866312262</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6649507692813401</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9999999982897825</v>
+        <v>0.9999946262773536</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9999999583063824</v>
+        <v>0.9999999026688069</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9999999810382185</v>
+        <v>0.9999993129615257</v>
       </c>
       <c r="G15" t="n">
-        <v>7.936281569357041e-09</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H15" t="n">
-        <v>0.198899696727747</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I15" t="n">
-        <v>1.614061309871944e-09</v>
+        <v>6.50011503440052e-07</v>
       </c>
       <c r="J15" t="n">
-        <v>3.187569909057724e-08</v>
+        <v>9.281554796456152e-08</v>
       </c>
       <c r="K15" t="n">
-        <v>1.674488020022459e-08</v>
+        <v>3.713185230149885e-07</v>
       </c>
       <c r="L15" t="n">
-        <v>1.684787686307017e-05</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>8.908581014593199e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000000007825624</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O15" t="n">
-        <v>9.287837751689409e-05</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P15" t="n">
-        <v>167.3036419751671</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q15" t="n">
-        <v>246.5305705916001</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_7_6_10</t>
+          <t>model_7_6_11</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9999999832217122</v>
+        <v>0.9999997997910529</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6649448705537726</v>
+        <v>0.7442000018021281</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9999999984823299</v>
+        <v>0.9999946262773536</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9999999464160279</v>
+        <v>0.9999999026688069</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9999999759943151</v>
+        <v>0.9999993129615257</v>
       </c>
       <c r="G16" t="n">
-        <v>9.960316381249069e-09</v>
+        <v>1.188526795810554e-07</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1989031984672429</v>
+        <v>0.1518539289148153</v>
       </c>
       <c r="I16" t="n">
-        <v>1.432339804714926e-09</v>
+        <v>6.50011503440052e-07</v>
       </c>
       <c r="J16" t="n">
-        <v>4.096613986673923e-08</v>
+        <v>9.281554796456152e-08</v>
       </c>
       <c r="K16" t="n">
-        <v>2.119907974032166e-08</v>
+        <v>3.713185230149885e-07</v>
       </c>
       <c r="L16" t="n">
-        <v>1.86293275370408e-05</v>
+        <v>6.47950546471013e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>9.980138466599082e-05</v>
+        <v>0.0003447501698056948</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000000009821437</v>
+        <v>1.000000117195481</v>
       </c>
       <c r="O16" t="n">
-        <v>0.000104050136228569</v>
+        <v>0.0003594268982655575</v>
       </c>
       <c r="P16" t="n">
-        <v>166.8493140013375</v>
+        <v>161.8907621949746</v>
       </c>
       <c r="Q16" t="n">
-        <v>246.0762426177706</v>
+        <v>241.1176908114076</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_7_6_9</t>
+          <t>model_7_6_8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.999999978972823</v>
+        <v>0.9999998003005452</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6649384795081004</v>
+        <v>0.7441998492308388</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9999999985163935</v>
+        <v>0.9999946372596451</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9999999318192682</v>
+        <v>0.9999999032023213</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9999999696921061</v>
+        <v>0.9999993146609902</v>
       </c>
       <c r="G17" t="n">
-        <v>1.248264061982259e-08</v>
+        <v>1.185502229087398e-07</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1989069924680326</v>
+        <v>0.1518540194877233</v>
       </c>
       <c r="I17" t="n">
-        <v>1.400191316451687e-09</v>
+        <v>6.486830731749834e-07</v>
       </c>
       <c r="J17" t="n">
-        <v>5.212568776243367e-08</v>
+        <v>9.230678564653577e-08</v>
       </c>
       <c r="K17" t="n">
-        <v>2.676447109403074e-08</v>
+        <v>3.704000261994245e-07</v>
       </c>
       <c r="L17" t="n">
-        <v>2.049719277675359e-05</v>
+        <v>6.501151645015302e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0001117257383946178</v>
+        <v>0.0003443112297162842</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000000012308591</v>
+        <v>1.000000116897242</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0001164821343822388</v>
+        <v>0.0003589692715878094</v>
       </c>
       <c r="P17" t="n">
-        <v>166.3978538165199</v>
+        <v>161.8958582882875</v>
       </c>
       <c r="Q17" t="n">
-        <v>245.6247824329529</v>
+        <v>241.1227869047205</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_7_6_8</t>
+          <t>model_7_6_9</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9999999735993007</v>
+        <v>0.9999998002326167</v>
       </c>
       <c r="C18" t="n">
-        <v>0.664930880900626</v>
+        <v>0.7441997833109575</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9999999984380508</v>
+        <v>0.999994635465065</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9999999133815154</v>
+        <v>0.9999999032332257</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9999999616719799</v>
+        <v>0.9999993141361864</v>
       </c>
       <c r="G18" t="n">
-        <v>1.567259558101109e-08</v>
+        <v>1.185905482255214e-07</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1989115033296722</v>
+        <v>0.1518540586206125</v>
       </c>
       <c r="I18" t="n">
-        <v>1.474129261867181e-09</v>
+        <v>6.489001475921092e-07</v>
       </c>
       <c r="J18" t="n">
-        <v>6.622176030762549e-08</v>
+        <v>9.227731507814253e-08</v>
       </c>
       <c r="K18" t="n">
-        <v>3.384693075454171e-08</v>
+        <v>3.706836629681703e-07</v>
       </c>
       <c r="L18" t="n">
-        <v>2.25794611760909e-05</v>
+        <v>6.4920670330104e-05</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0001251902375627233</v>
+        <v>0.0003443697841354862</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000000015454068</v>
+        <v>1.000000116937005</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0001305198451552862</v>
+        <v>0.0003590303187898612</v>
       </c>
       <c r="P18" t="n">
-        <v>165.9427043083084</v>
+        <v>161.8951780962314</v>
       </c>
       <c r="Q18" t="n">
-        <v>245.1696329247414</v>
+        <v>241.1221067126645</v>
       </c>
     </row>
     <row r="19">
@@ -1452,52 +1452,52 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9999999668458154</v>
+        <v>0.9999989168288207</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6649224992887769</v>
+        <v>0.7439543805673152</v>
       </c>
       <c r="D19" t="n">
-        <v>0.999999998117314</v>
+        <v>0.9999999768241161</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9999998902171054</v>
+        <v>0.9999999519603764</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9999999514731723</v>
+        <v>0.9999999550253489</v>
       </c>
       <c r="G19" t="n">
-        <v>1.968175619085979e-08</v>
+        <v>6.430172026105757e-07</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1989164790165326</v>
+        <v>0.1519997402900851</v>
       </c>
       <c r="I19" t="n">
-        <v>1.776832837643234e-09</v>
+        <v>2.803380842378311e-09</v>
       </c>
       <c r="J19" t="n">
-        <v>8.393146750705058e-08</v>
+        <v>4.58108428020295e-08</v>
       </c>
       <c r="K19" t="n">
-        <v>4.28533530065366e-08</v>
+        <v>2.430711182220391e-08</v>
       </c>
       <c r="L19" t="n">
-        <v>2.495047108048535e-05</v>
+        <v>0.0002737046385990106</v>
       </c>
       <c r="M19" t="n">
-        <v>0.000140291682543406</v>
+        <v>0.000801883534318155</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000000019407328</v>
+        <v>1.000000634051422</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0001462641899130972</v>
+        <v>0.0008360213765018315</v>
       </c>
       <c r="P19" t="n">
-        <v>165.4871474239266</v>
+        <v>158.5141887187909</v>
       </c>
       <c r="Q19" t="n">
-        <v>244.7140760403596</v>
+        <v>237.741117335224</v>
       </c>
     </row>
     <row r="20">
@@ -1507,52 +1507,52 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9999999584639906</v>
+        <v>0.9999987283284677</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6649129724370965</v>
+        <v>0.7438954869802874</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9999999975656583</v>
+        <v>0.9999999999997147</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9999998615774353</v>
+        <v>0.9999998940936049</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9999999387804119</v>
+        <v>0.9999999065679914</v>
       </c>
       <c r="G20" t="n">
-        <v>2.465756945243257e-08</v>
+        <v>7.549191549090759e-07</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1989221345672287</v>
+        <v>0.1520347020674153</v>
       </c>
       <c r="I20" t="n">
-        <v>2.297471911603473e-09</v>
+        <v>3.450952035594287e-14</v>
       </c>
       <c r="J20" t="n">
-        <v>1.058271331266073e-07</v>
+        <v>1.009929064959202e-07</v>
       </c>
       <c r="K20" t="n">
-        <v>5.406214960355726e-08</v>
+        <v>5.049649580088272e-08</v>
       </c>
       <c r="L20" t="n">
-        <v>2.750363538881155e-05</v>
+        <v>0.0002722314288240303</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0001570272888781837</v>
+        <v>0.0008688608374815128</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000000024313762</v>
+        <v>1.000000744393092</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0001637122656570275</v>
+        <v>0.0009058500421229845</v>
       </c>
       <c r="P20" t="n">
-        <v>165.0363638128369</v>
+        <v>158.1933103460429</v>
       </c>
       <c r="Q20" t="n">
-        <v>244.26329242927</v>
+        <v>237.4202389624759</v>
       </c>
     </row>
     <row r="21">
@@ -1562,52 +1562,52 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9999999479876924</v>
+        <v>0.9999987283284677</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6649021687821566</v>
+        <v>0.74389548570271</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9999999967210131</v>
+        <v>0.9999999999997147</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9999998258772399</v>
+        <v>0.9999998940936049</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9999999228764643</v>
+        <v>0.9999999065679914</v>
       </c>
       <c r="G21" t="n">
-        <v>3.087675257533404e-08</v>
+        <v>7.549191549090759e-07</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1989285480834945</v>
+        <v>0.1520347028258405</v>
       </c>
       <c r="I21" t="n">
-        <v>3.094627266542238e-09</v>
+        <v>3.450952035594287e-14</v>
       </c>
       <c r="J21" t="n">
-        <v>1.331207274013403e-07</v>
+        <v>1.009929064959202e-07</v>
       </c>
       <c r="K21" t="n">
-        <v>6.810670007711707e-08</v>
+        <v>5.049649580088272e-08</v>
       </c>
       <c r="L21" t="n">
-        <v>3.040900474293171e-05</v>
+        <v>0.0002722314288240303</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0001757178208814747</v>
+        <v>0.0008688608374815128</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000000030446229</v>
+        <v>1.000000744393092</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0001831984923024336</v>
+        <v>0.0009058500421229845</v>
       </c>
       <c r="P21" t="n">
-        <v>164.5865245600714</v>
+        <v>158.1933103460429</v>
       </c>
       <c r="Q21" t="n">
-        <v>243.8134531765044</v>
+        <v>237.4202389624759</v>
       </c>
     </row>
     <row r="22">
@@ -1617,52 +1617,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9999999348615124</v>
+        <v>0.9999987283284677</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6648902033098272</v>
+        <v>0.7438954833271847</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9999999954992932</v>
+        <v>0.9999999999997147</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9999997811327075</v>
+        <v>0.9999998940936049</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9999999028539622</v>
+        <v>0.9999999065679914</v>
       </c>
       <c r="G22" t="n">
-        <v>3.866902005238697e-08</v>
+        <v>7.549191549090759e-07</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1989356513047508</v>
+        <v>0.1520347042360549</v>
       </c>
       <c r="I22" t="n">
-        <v>4.247656471494468e-09</v>
+        <v>3.450952035594287e-14</v>
       </c>
       <c r="J22" t="n">
-        <v>1.673289187752133e-07</v>
+        <v>1.009929064959202e-07</v>
       </c>
       <c r="K22" t="n">
-        <v>8.578828762335387e-08</v>
+        <v>5.049649580088272e-08</v>
       </c>
       <c r="L22" t="n">
-        <v>3.378002312321145e-05</v>
+        <v>0.0002722314288240303</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0001966444000026112</v>
+        <v>0.0008688608374815128</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000000038129846</v>
+        <v>1.000000744393092</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0002050159592207476</v>
+        <v>0.0009058500421229845</v>
       </c>
       <c r="P22" t="n">
-        <v>164.1364541458729</v>
+        <v>158.1933103460429</v>
       </c>
       <c r="Q22" t="n">
-        <v>243.3633827623059</v>
+        <v>237.4202389624759</v>
       </c>
     </row>
     <row r="23">
@@ -1672,217 +1672,217 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9999999185864762</v>
+        <v>0.9999987283082314</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6648760937966915</v>
+        <v>0.7438954810871585</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9999999937659534</v>
+        <v>0.999999999999444</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9999997257248161</v>
+        <v>0.9999998940149342</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9999998779430181</v>
+        <v>0.9999999064985567</v>
       </c>
       <c r="G23" t="n">
-        <v>4.833058463265381e-08</v>
+        <v>7.549311680361854e-07</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1989440273212474</v>
+        <v>0.1520347055658312</v>
       </c>
       <c r="I23" t="n">
-        <v>5.883540074477769e-09</v>
+        <v>6.725807408657651e-14</v>
       </c>
       <c r="J23" t="n">
-        <v>2.096894855887115e-07</v>
+        <v>1.010679273700926e-07</v>
       </c>
       <c r="K23" t="n">
-        <v>1.077867888458779e-07</v>
+        <v>5.053402261224581e-08</v>
       </c>
       <c r="L23" t="n">
-        <v>3.780060418687985e-05</v>
+        <v>0.0002722407227971125</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0002198421811951787</v>
+        <v>0.0008688677506020036</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000000047656697</v>
+        <v>1.000000744404938</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0002292013179847098</v>
+        <v>0.0009058572495493267</v>
       </c>
       <c r="P23" t="n">
-        <v>163.6904025089606</v>
+        <v>158.1932785200349</v>
       </c>
       <c r="Q23" t="n">
-        <v>242.9173311253937</v>
+        <v>237.420207136468</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_7_6_0</t>
+          <t>model_7_6_2</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9999998847070766</v>
+        <v>0.9999987283082314</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6648690401964312</v>
+        <v>0.7438954804054183</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9999999937142722</v>
+        <v>0.999999999999444</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9999996163986367</v>
+        <v>0.9999998940149342</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9999998305917184</v>
+        <v>0.9999999064985567</v>
       </c>
       <c r="G24" t="n">
-        <v>6.844285971645804e-08</v>
+        <v>7.549311680361854e-07</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1989482146430616</v>
+        <v>0.1520347059705416</v>
       </c>
       <c r="I24" t="n">
-        <v>5.93231548574258e-09</v>
+        <v>6.725807408657651e-14</v>
       </c>
       <c r="J24" t="n">
-        <v>2.932717842053961e-07</v>
+        <v>1.010679273700926e-07</v>
       </c>
       <c r="K24" t="n">
-        <v>1.496020498455694e-07</v>
+        <v>5.053402261224581e-08</v>
       </c>
       <c r="L24" t="n">
-        <v>4.274244929839192e-05</v>
+        <v>0.0002722407227971125</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0002616158628914884</v>
+        <v>0.0008688677506020036</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000000067488541</v>
+        <v>1.000000744404938</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0002727533917942735</v>
+        <v>0.0009058572495493267</v>
       </c>
       <c r="P24" t="n">
-        <v>162.9945332090209</v>
+        <v>158.1932785200349</v>
       </c>
       <c r="Q24" t="n">
-        <v>242.221461825454</v>
+        <v>237.420207136468</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_7_6_1</t>
+          <t>model_7_6_0</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9999998847070649</v>
+        <v>0.9999987283082538</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6648690384099278</v>
+        <v>0.74389547539695</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9999999937142722</v>
+        <v>0.9999999999994845</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9999996163986455</v>
+        <v>0.9999998939362336</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9999998305917223</v>
+        <v>0.9999999064291307</v>
       </c>
       <c r="G25" t="n">
-        <v>6.844286666116335e-08</v>
+        <v>7.549311547896211e-07</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1989482157036071</v>
+        <v>0.1520347089437847</v>
       </c>
       <c r="I25" t="n">
-        <v>5.93231548574258e-09</v>
+        <v>6.234741418033642e-14</v>
       </c>
       <c r="J25" t="n">
-        <v>2.932717773976886e-07</v>
+        <v>1.011429766659745e-07</v>
       </c>
       <c r="K25" t="n">
-        <v>1.496020464417156e-07</v>
+        <v>5.057154480485679e-08</v>
       </c>
       <c r="L25" t="n">
-        <v>4.273997585580924e-05</v>
+        <v>0.000272216221254117</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0002616158761642025</v>
+        <v>0.0008688677429791148</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000000067488547</v>
+        <v>1.000000744404925</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0002727534056320346</v>
+        <v>0.0009058572416019158</v>
       </c>
       <c r="P25" t="n">
-        <v>162.9945330060866</v>
+        <v>158.1932785551283</v>
       </c>
       <c r="Q25" t="n">
-        <v>242.2214616225196</v>
+        <v>237.4202071715614</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_7_6_2</t>
+          <t>model_7_6_1</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9999998985145444</v>
+        <v>0.9999987283082328</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6648612403765572</v>
+        <v>0.7438954750300184</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9999999916567974</v>
+        <v>0.9999999999994845</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9999996573948619</v>
+        <v>0.9999998939362336</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9999998472383073</v>
+        <v>0.9999999064291307</v>
       </c>
       <c r="G26" t="n">
-        <v>6.02461503922018e-08</v>
+        <v>7.549311672504798e-07</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1989528449530734</v>
+        <v>0.1520347091616112</v>
       </c>
       <c r="I26" t="n">
-        <v>7.874109598262092e-09</v>
+        <v>6.234741418033642e-14</v>
       </c>
       <c r="J26" t="n">
-        <v>2.619292571610111e-07</v>
+        <v>1.011429766659745e-07</v>
       </c>
       <c r="K26" t="n">
-        <v>1.349016833796366e-07</v>
+        <v>5.057154480485679e-08</v>
       </c>
       <c r="L26" t="n">
-        <v>4.216030507067267e-05</v>
+        <v>0.0002722376605827484</v>
       </c>
       <c r="M26" t="n">
-        <v>0.000245450912388204</v>
+        <v>0.0008688677501498601</v>
       </c>
       <c r="N26" t="n">
-        <v>1.00000005940612</v>
+        <v>1.000000744404937</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0002559002658820037</v>
+        <v>0.0009058572490779346</v>
       </c>
       <c r="P26" t="n">
-        <v>163.2496543210446</v>
+        <v>158.1932785221164</v>
       </c>
       <c r="Q26" t="n">
-        <v>242.4765829374777</v>
+        <v>237.4202071385495</v>
       </c>
     </row>
   </sheetData>
